--- a/artfynd/A 52261-2022 artfynd.xlsx
+++ b/artfynd/A 52261-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52261-2022 artfynd.xlsx
+++ b/artfynd/A 52261-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104942543</v>
+        <v>104942546</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662894.8326168132</v>
+        <v>662893</v>
       </c>
       <c r="R2" t="n">
-        <v>6523591.999503975</v>
+        <v>6523426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107527336</v>
+        <v>107525871</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662854.5873597423</v>
+        <v>662851</v>
       </c>
       <c r="R3" t="n">
-        <v>6523585.636703936</v>
+        <v>6523408</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,7 +843,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +853,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107526205</v>
+        <v>107526238</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +891,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662812.9441571129</v>
+        <v>662812</v>
       </c>
       <c r="R4" t="n">
-        <v>6523563.142883749</v>
+        <v>6523564</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,7 +951,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +961,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,51 +988,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107526238</v>
+        <v>107526632</v>
       </c>
       <c r="B5" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spikhammar, Srm</t>
+          <t>Langinge, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662811.8635669583</v>
+        <v>662780</v>
       </c>
       <c r="R5" t="n">
-        <v>6523564.134287199</v>
+        <v>6523642</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,7 +1059,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1069,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,15 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107526632</v>
+        <v>107526805</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1124,16 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662778.9954766871</v>
+        <v>662794</v>
       </c>
       <c r="R6" t="n">
-        <v>6523641.55592248</v>
+        <v>6523712</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1210,427 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107526837</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Langinge, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>662794</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6523712</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>107527336</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spikhammar, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>662855</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6523585</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104942543</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gabrielstorp, Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>662895</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6523592</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>107526205</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spikhammar, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>662813</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6523563</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52261-2022 artfynd.xlsx
+++ b/artfynd/A 52261-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104942546</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107525871</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107526238</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107526632</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107526805</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107526837</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107527336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104942543</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,8 +1676,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107526205</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>